--- a/rules/CORE-000238/negative/01/data/unit-test-coreid-CG0147-negative 1.xlsx
+++ b/rules/CORE-000238/negative/01/data/unit-test-coreid-CG0147-negative 1.xlsx
@@ -83,7 +83,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -135,6 +135,11 @@
         <fgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -155,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -171,6 +176,7 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -661,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,7 +788,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -794,10 +800,8 @@
           <t>Record</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="D5" t="n">
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -807,6 +811,141 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>2014-01-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ex.xpt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>61</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>$max_ex_exstdtc</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2014-01-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ex.xpt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>61</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>$max_ex_exendtc</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2014-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>dm.xpt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RFXENDTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ex.xpt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>63</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>$max_ex_exstdtc</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2014-01-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ex.xpt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>63</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>$max_ex_exendtc</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -821,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1446,7 +1585,7 @@
           <t>2014-01-01</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>2014-01-10</t>
         </is>
@@ -1515,6 +1654,112 @@
         </is>
       </c>
       <c r="Z6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GUARD-RFXEN-NULL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2012-11-30</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2013-01-23</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2012-11-23</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2013-05-20</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>84</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>YEARS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>WHITE</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NOT HISPANIC OR LATINO</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>ZAN_LOW</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Zanomaline Low Dose (54 mg)</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>ZAN_LOW</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Zanomaline Low Dose (54 mg)</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
@@ -1531,7 +1776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6351,6 +6596,164 @@
         <v>1</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>EX</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>GUARD-RFXEN-NULL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DEV0001</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ZANOMALINE</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>54</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>QD</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>SUBCUTANEOUS</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>SDS580-359</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2014-01-05</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>EX</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>GUARD-RFXEN-NULL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DEV0001</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>ZANOMALINE</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>54</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>QD</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>SUBCUTANEOUS</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>SDS580-359</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2014-01-10</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2014-01-20</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rules/CORE-000238/negative/01/data/unit-test-coreid-CG0147-negative 1.xlsx
+++ b/rules/CORE-000238/negative/01/data/unit-test-coreid-CG0147-negative 1.xlsx
@@ -160,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -177,6 +177,7 @@
     <xf numFmtId="0" fontId="12" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -667,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,6 +947,85 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>2014-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>dm.xpt</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RFXENDTC</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2014-01-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ex.xpt</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>65</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>$max_ex_exstdtc</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2014-01-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ex.xpt</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>65</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>$max_ex_exendtc</t>
         </is>
       </c>
     </row>
@@ -960,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1760,6 +1840,116 @@
         </is>
       </c>
       <c r="Z7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GUARD-NO-EXEN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2012-11-30</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2013-01-23</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>2014-01-15</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2012-11-23</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2013-05-20</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>84</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>YEARS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>WHITE</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NOT HISPANIC OR LATINO</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>ZAN_LOW</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Zanomaline Low Dose (54 mg)</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>ZAN_LOW</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Zanomaline Low Dose (54 mg)</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
@@ -1776,7 +1966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:Q65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6754,6 +6944,154 @@
         <v>1</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>EX</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>GUARD-NO-EXEN</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DEV0001</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ZANOMALINE</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>54</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>QD</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>SUBCUTANEOUS</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>SDS580-359</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>EX</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>GUARD-NO-EXEN</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DEV0001</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ZANOMALINE</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>54</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>QD</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>SUBCUTANEOUS</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>SDS580-359</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>2014-01-10</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
